--- a/4.1 Myrmidon Happy reef/output/yearly_population_growth_param_0.5.xlsx
+++ b/4.1 Myrmidon Happy reef/output/yearly_population_growth_param_0.5.xlsx
@@ -772,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41382</v>
+        <v>43085</v>
       </c>
       <c r="C2" t="n">
-        <v>2789</v>
+        <v>2354</v>
       </c>
       <c r="D2" t="n">
-        <v>143494</v>
+        <v>108156</v>
       </c>
     </row>
     <row r="3">
@@ -786,13 +786,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22378</v>
+        <v>22998</v>
       </c>
       <c r="C3" t="n">
-        <v>2464</v>
+        <v>2115</v>
       </c>
       <c r="D3" t="n">
-        <v>29332</v>
+        <v>23147</v>
       </c>
     </row>
     <row r="4">
@@ -800,13 +800,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11522</v>
+        <v>11879</v>
       </c>
       <c r="C4" t="n">
-        <v>1923</v>
+        <v>1645</v>
       </c>
       <c r="D4" t="n">
-        <v>6545</v>
+        <v>5987</v>
       </c>
     </row>
     <row r="5">
@@ -814,13 +814,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6847</v>
+        <v>6929</v>
       </c>
       <c r="C5" t="n">
-        <v>891</v>
+        <v>778</v>
       </c>
       <c r="D5" t="n">
-        <v>1814</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="6">
@@ -828,13 +828,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4469</v>
+        <v>4525</v>
       </c>
       <c r="C6" t="n">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="D6" t="n">
-        <v>1325</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="7">
@@ -842,13 +842,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2547</v>
+        <v>2624</v>
       </c>
       <c r="C7" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D7" t="n">
-        <v>1002</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="8">
@@ -856,13 +856,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1150</v>
+        <v>1272</v>
       </c>
       <c r="C8" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D8" t="n">
-        <v>889</v>
+        <v>898</v>
       </c>
     </row>
     <row r="9">
@@ -870,13 +870,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>333</v>
+        <v>419</v>
       </c>
       <c r="C9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D9" t="n">
-        <v>795</v>
+        <v>816</v>
       </c>
     </row>
     <row r="10">
@@ -884,13 +884,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10" t="n">
-        <v>718</v>
+        <v>707</v>
       </c>
     </row>
     <row r="11">
@@ -898,13 +898,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D11" t="n">
-        <v>595</v>
+        <v>607</v>
       </c>
     </row>
     <row r="12">
@@ -912,13 +912,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D12" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13">
@@ -926,13 +926,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14">
@@ -940,13 +940,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15">
@@ -954,13 +954,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16">
@@ -968,13 +968,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17">
@@ -982,13 +982,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -996,13 +996,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1010,13 +1010,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1083,13 +1083,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>55633</v>
+        <v>57810</v>
       </c>
       <c r="C2" t="n">
-        <v>2549</v>
+        <v>2130</v>
       </c>
       <c r="D2" t="n">
-        <v>120928</v>
+        <v>90954</v>
       </c>
     </row>
     <row r="3">
@@ -1097,13 +1097,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28803</v>
+        <v>29904</v>
       </c>
       <c r="C3" t="n">
-        <v>2362</v>
+        <v>2021</v>
       </c>
       <c r="D3" t="n">
-        <v>32772</v>
+        <v>25658</v>
       </c>
     </row>
     <row r="4">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16406</v>
+        <v>16771</v>
       </c>
       <c r="C4" t="n">
-        <v>1963</v>
+        <v>1680</v>
       </c>
       <c r="D4" t="n">
-        <v>7221</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="5">
@@ -1125,13 +1125,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>8841</v>
+        <v>9038</v>
       </c>
       <c r="C5" t="n">
-        <v>1059</v>
+        <v>911</v>
       </c>
       <c r="D5" t="n">
-        <v>1925</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="6">
@@ -1139,13 +1139,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5610</v>
+        <v>5681</v>
       </c>
       <c r="C6" t="n">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="D6" t="n">
-        <v>1322</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="7">
@@ -1153,13 +1153,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3435</v>
+        <v>3505</v>
       </c>
       <c r="C7" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D7" t="n">
-        <v>997</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="8">
@@ -1167,13 +1167,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1733</v>
+        <v>1883</v>
       </c>
       <c r="C8" t="n">
         <v>96</v>
       </c>
       <c r="D8" t="n">
-        <v>883</v>
+        <v>892</v>
       </c>
     </row>
     <row r="9">
@@ -1181,13 +1181,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>635</v>
+        <v>773</v>
       </c>
       <c r="C9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" t="n">
-        <v>795</v>
+        <v>807</v>
       </c>
     </row>
     <row r="10">
@@ -1195,13 +1195,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D10" t="n">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="11">
@@ -1209,13 +1209,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C11" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D11" t="n">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12">
@@ -1223,13 +1223,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D12" t="n">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13">
@@ -1237,13 +1237,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14">
@@ -1251,13 +1251,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15">
@@ -1268,10 +1268,10 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16">
@@ -1279,13 +1279,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17">
@@ -1293,13 +1293,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -1307,13 +1307,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1321,10 +1321,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -1394,13 +1394,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>69563</v>
+        <v>72150</v>
       </c>
       <c r="C2" t="n">
-        <v>1891</v>
+        <v>1573</v>
       </c>
       <c r="D2" t="n">
-        <v>143713</v>
+        <v>107106</v>
       </c>
     </row>
     <row r="3">
@@ -1408,13 +1408,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>37563</v>
+        <v>39280</v>
       </c>
       <c r="C3" t="n">
-        <v>2246</v>
+        <v>1914</v>
       </c>
       <c r="D3" t="n">
-        <v>34386</v>
+        <v>26803</v>
       </c>
     </row>
     <row r="4">
@@ -1422,13 +1422,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21331</v>
+        <v>21654</v>
       </c>
       <c r="C4" t="n">
-        <v>1991</v>
+        <v>1703</v>
       </c>
       <c r="D4" t="n">
-        <v>7737</v>
+        <v>6819</v>
       </c>
     </row>
     <row r="5">
@@ -1436,13 +1436,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11864</v>
+        <v>12104</v>
       </c>
       <c r="C5" t="n">
-        <v>1175</v>
+        <v>1001</v>
       </c>
       <c r="D5" t="n">
-        <v>1981</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="6">
@@ -1450,13 +1450,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7054</v>
+        <v>7196</v>
       </c>
       <c r="C6" t="n">
-        <v>479</v>
+        <v>440</v>
       </c>
       <c r="D6" t="n">
-        <v>1320</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="7">
@@ -1464,13 +1464,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4349</v>
+        <v>4413</v>
       </c>
       <c r="C7" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D7" t="n">
-        <v>992</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
@@ -1478,13 +1478,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2357</v>
+        <v>2546</v>
       </c>
       <c r="C8" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" t="n">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="9">
@@ -1492,13 +1492,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1007</v>
+        <v>1183</v>
       </c>
       <c r="C9" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D9" t="n">
-        <v>786</v>
+        <v>798</v>
       </c>
     </row>
     <row r="10">
@@ -1506,13 +1506,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>296</v>
+        <v>412</v>
       </c>
       <c r="C10" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>690</v>
+        <v>696</v>
       </c>
     </row>
     <row r="11">
@@ -1520,13 +1520,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="C11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D11" t="n">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="12">
@@ -1534,13 +1534,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C12" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="13">
@@ -1548,13 +1548,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="14">
@@ -1565,10 +1565,10 @@
         <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15">
@@ -1576,13 +1576,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16">
@@ -1590,13 +1590,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17">
@@ -1604,13 +1604,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
@@ -1618,13 +1618,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
+        <v>18</v>
+      </c>
+      <c r="D18" t="n">
         <v>11</v>
-      </c>
-      <c r="D18" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -1632,10 +1632,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1705,13 +1705,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3761</v>
+        <v>3679</v>
       </c>
       <c r="C2" t="n">
-        <v>4251</v>
+        <v>3661</v>
       </c>
       <c r="D2" t="n">
-        <v>16346</v>
+        <v>13429</v>
       </c>
     </row>
     <row r="3">
@@ -1733,10 +1733,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D4" t="n">
         <v>5056</v>
@@ -1761,13 +1761,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n">
         <v>94</v>
       </c>
       <c r="D6" t="n">
-        <v>1147</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="7">
@@ -1778,10 +1778,10 @@
         <v>66</v>
       </c>
       <c r="C7" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D7" t="n">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="8">
@@ -1795,7 +1795,7 @@
         <v>79</v>
       </c>
       <c r="D8" t="n">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="9">
@@ -1809,7 +1809,7 @@
         <v>70</v>
       </c>
       <c r="D9" t="n">
-        <v>855</v>
+        <v>863</v>
       </c>
     </row>
     <row r="10">
@@ -1823,7 +1823,7 @@
         <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>757</v>
+        <v>751</v>
       </c>
     </row>
     <row r="11">
@@ -1834,10 +1834,10 @@
         <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="12">
@@ -1845,13 +1845,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="13">
@@ -1862,10 +1862,10 @@
         <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14">
@@ -1879,7 +1879,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15">
@@ -1887,13 +1887,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16">
@@ -1907,7 +1907,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17">
@@ -1915,13 +1915,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18">
@@ -1929,13 +1929,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
         <v>38</v>
       </c>
       <c r="D18" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19">
@@ -1949,7 +1949,7 @@
         <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20">
@@ -1960,10 +1960,10 @@
         <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -1971,10 +1971,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2016,13 +2016,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5462</v>
+        <v>5450</v>
       </c>
       <c r="C2" t="n">
-        <v>4762</v>
+        <v>4107</v>
       </c>
       <c r="D2" t="n">
-        <v>60082</v>
+        <v>46794</v>
       </c>
     </row>
     <row r="3">
@@ -2030,13 +2030,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2410</v>
+        <v>2357</v>
       </c>
       <c r="C3" t="n">
-        <v>917</v>
+        <v>804</v>
       </c>
       <c r="D3" t="n">
-        <v>6399</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="4">
@@ -2044,10 +2044,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D4" t="n">
         <v>5010</v>
@@ -2058,10 +2058,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D5" t="n">
         <v>1374</v>
@@ -2072,13 +2072,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n">
         <v>97</v>
       </c>
       <c r="D6" t="n">
-        <v>1169</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="7">
@@ -2086,13 +2086,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" t="n">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="8">
@@ -2100,13 +2100,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
         <v>80</v>
       </c>
       <c r="D8" t="n">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="9">
@@ -2120,7 +2120,7 @@
         <v>71</v>
       </c>
       <c r="D9" t="n">
-        <v>846</v>
+        <v>854</v>
       </c>
     </row>
     <row r="10">
@@ -2134,7 +2134,7 @@
         <v>63</v>
       </c>
       <c r="D10" t="n">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="11">
@@ -2142,13 +2142,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D11" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="12">
@@ -2156,13 +2156,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="13">
@@ -2170,13 +2170,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="14">
@@ -2190,7 +2190,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15">
@@ -2198,13 +2198,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16">
@@ -2212,13 +2212,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17">
@@ -2226,13 +2226,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18">
@@ -2240,13 +2240,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
         <v>39</v>
       </c>
       <c r="D18" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19">
@@ -2257,7 +2257,7 @@
         <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D19" t="n">
         <v>85</v>
@@ -2268,13 +2268,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -2327,13 +2327,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5993</v>
+        <v>6107</v>
       </c>
       <c r="C2" t="n">
-        <v>4160</v>
+        <v>3585</v>
       </c>
       <c r="D2" t="n">
-        <v>66328</v>
+        <v>51363</v>
       </c>
     </row>
     <row r="3">
@@ -2341,13 +2341,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3926</v>
+        <v>3909</v>
       </c>
       <c r="C3" t="n">
-        <v>1592</v>
+        <v>1382</v>
       </c>
       <c r="D3" t="n">
-        <v>8239</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="4">
@@ -2355,13 +2355,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1627</v>
+        <v>1591</v>
       </c>
       <c r="C4" t="n">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="D4" t="n">
-        <v>4972</v>
+        <v>4966</v>
       </c>
     </row>
     <row r="5">
@@ -2369,10 +2369,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D5" t="n">
         <v>1436</v>
@@ -2383,13 +2383,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D6" t="n">
-        <v>1192</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="7">
@@ -2397,13 +2397,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D7" t="n">
-        <v>1032</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="8">
@@ -2411,13 +2411,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
-        <v>925</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9">
@@ -2425,13 +2425,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
         <v>72</v>
       </c>
       <c r="D9" t="n">
-        <v>838</v>
+        <v>846</v>
       </c>
     </row>
     <row r="10">
@@ -2445,7 +2445,7 @@
         <v>64</v>
       </c>
       <c r="D10" t="n">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="11">
@@ -2453,13 +2453,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D11" t="n">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="12">
@@ -2467,13 +2467,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>542</v>
+        <v>553</v>
       </c>
     </row>
     <row r="13">
@@ -2481,13 +2481,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14">
@@ -2501,7 +2501,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15">
@@ -2509,7 +2509,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
         <v>38</v>
@@ -2523,13 +2523,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17">
@@ -2537,13 +2537,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18">
@@ -2551,13 +2551,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D18" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19">
@@ -2565,13 +2565,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -2579,13 +2579,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -2638,13 +2638,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8855</v>
+        <v>8905</v>
       </c>
       <c r="C2" t="n">
-        <v>5569</v>
+        <v>4795</v>
       </c>
       <c r="D2" t="n">
-        <v>107724</v>
+        <v>82786</v>
       </c>
     </row>
     <row r="3">
@@ -2652,13 +2652,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4585</v>
+        <v>4656</v>
       </c>
       <c r="C3" t="n">
-        <v>1975</v>
+        <v>1709</v>
       </c>
       <c r="D3" t="n">
-        <v>10167</v>
+        <v>8985</v>
       </c>
     </row>
     <row r="4">
@@ -2666,13 +2666,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3002</v>
+        <v>2956</v>
       </c>
       <c r="C4" t="n">
-        <v>601</v>
+        <v>535</v>
       </c>
       <c r="D4" t="n">
-        <v>5025</v>
+        <v>4989</v>
       </c>
     </row>
     <row r="5">
@@ -2680,10 +2680,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="C5" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D5" t="n">
         <v>1494</v>
@@ -2694,13 +2694,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D6" t="n">
-        <v>1215</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="7">
@@ -2708,13 +2708,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D7" t="n">
-        <v>1027</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="8">
@@ -2722,13 +2722,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D8" t="n">
-        <v>919</v>
+        <v>923</v>
       </c>
     </row>
     <row r="9">
@@ -2736,13 +2736,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" t="n">
-        <v>830</v>
+        <v>838</v>
       </c>
     </row>
     <row r="10">
@@ -2756,7 +2756,7 @@
         <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="11">
@@ -2767,10 +2767,10 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D11" t="n">
-        <v>640</v>
+        <v>650</v>
       </c>
     </row>
     <row r="12">
@@ -2778,13 +2778,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="13">
@@ -2792,13 +2792,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14">
@@ -2812,7 +2812,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15">
@@ -2820,10 +2820,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>323</v>
@@ -2834,13 +2834,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17">
@@ -2848,13 +2848,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18">
@@ -2862,13 +2862,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D18" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19">
@@ -2876,13 +2876,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -2890,13 +2890,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -2949,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12150</v>
+        <v>12320</v>
       </c>
       <c r="C2" t="n">
-        <v>4543</v>
+        <v>3910</v>
       </c>
       <c r="D2" t="n">
-        <v>106709</v>
+        <v>81758</v>
       </c>
     </row>
     <row r="3">
@@ -2963,13 +2963,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6487</v>
+        <v>6532</v>
       </c>
       <c r="C3" t="n">
-        <v>2529</v>
+        <v>2183</v>
       </c>
       <c r="D3" t="n">
-        <v>13581</v>
+        <v>11505</v>
       </c>
     </row>
     <row r="4">
@@ -2977,13 +2977,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3751</v>
+        <v>3763</v>
       </c>
       <c r="C4" t="n">
-        <v>891</v>
+        <v>783</v>
       </c>
       <c r="D4" t="n">
-        <v>5167</v>
+        <v>5077</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2198</v>
+        <v>2167</v>
       </c>
       <c r="C5" t="n">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="D5" t="n">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="6">
@@ -3005,13 +3005,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>664</v>
+        <v>692</v>
       </c>
       <c r="C6" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D6" t="n">
-        <v>1239</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="7">
@@ -3019,13 +3019,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C7" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D7" t="n">
-        <v>1022</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="8">
@@ -3033,13 +3033,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" t="n">
-        <v>913</v>
+        <v>918</v>
       </c>
     </row>
     <row r="9">
@@ -3047,13 +3047,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D9" t="n">
-        <v>823</v>
+        <v>831</v>
       </c>
     </row>
     <row r="10">
@@ -3061,13 +3061,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
         <v>66</v>
       </c>
       <c r="D10" t="n">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="11">
@@ -3078,10 +3078,10 @@
         <v>45</v>
       </c>
       <c r="C11" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D11" t="n">
-        <v>631</v>
+        <v>642</v>
       </c>
     </row>
     <row r="12">
@@ -3089,13 +3089,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>524</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13">
@@ -3103,13 +3103,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14">
@@ -3117,13 +3117,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15">
@@ -3131,10 +3131,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>308</v>
@@ -3145,13 +3145,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17">
@@ -3159,13 +3159,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18">
@@ -3173,13 +3173,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>41</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
@@ -3187,13 +3187,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -3201,10 +3201,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
@@ -3260,13 +3260,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14423</v>
+        <v>14928</v>
       </c>
       <c r="C2" t="n">
-        <v>4069</v>
+        <v>3493</v>
       </c>
       <c r="D2" t="n">
-        <v>121690</v>
+        <v>92847</v>
       </c>
     </row>
     <row r="3">
@@ -3274,13 +3274,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8894</v>
+        <v>9109</v>
       </c>
       <c r="C3" t="n">
-        <v>2741</v>
+        <v>2364</v>
       </c>
       <c r="D3" t="n">
-        <v>16784</v>
+        <v>13873</v>
       </c>
     </row>
     <row r="4">
@@ -3288,13 +3288,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>5142</v>
       </c>
       <c r="C4" t="n">
-        <v>1234</v>
+        <v>1075</v>
       </c>
       <c r="D4" t="n">
-        <v>5333</v>
+        <v>5169</v>
       </c>
     </row>
     <row r="5">
@@ -3302,13 +3302,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2982</v>
+        <v>2985</v>
       </c>
       <c r="C5" t="n">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="D5" t="n">
-        <v>1607</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="6">
@@ -3316,13 +3316,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1614</v>
+        <v>1639</v>
       </c>
       <c r="C6" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D6" t="n">
-        <v>1264</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="7">
@@ -3330,13 +3330,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="C7" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D7" t="n">
-        <v>1017</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="8">
@@ -3344,13 +3344,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D8" t="n">
-        <v>907</v>
+        <v>913</v>
       </c>
     </row>
     <row r="9">
@@ -3358,13 +3358,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D9" t="n">
-        <v>816</v>
+        <v>824</v>
       </c>
     </row>
     <row r="10">
@@ -3372,13 +3372,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
         <v>67</v>
       </c>
       <c r="D10" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="11">
@@ -3389,10 +3389,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D11" t="n">
-        <v>622</v>
+        <v>634</v>
       </c>
     </row>
     <row r="12">
@@ -3400,13 +3400,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>517</v>
+        <v>524</v>
       </c>
     </row>
     <row r="13">
@@ -3414,13 +3414,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14">
@@ -3428,13 +3428,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15">
@@ -3442,10 +3442,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>292</v>
@@ -3456,10 +3456,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>207</v>
@@ -3470,13 +3470,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18">
@@ -3484,13 +3484,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
@@ -3498,13 +3498,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
+        <v>27</v>
+      </c>
+      <c r="D19" t="n">
         <v>19</v>
-      </c>
-      <c r="D19" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -3512,10 +3512,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -3571,13 +3571,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20886</v>
+        <v>21759</v>
       </c>
       <c r="C2" t="n">
-        <v>3335</v>
+        <v>2850</v>
       </c>
       <c r="D2" t="n">
-        <v>153251</v>
+        <v>116330</v>
       </c>
     </row>
     <row r="3">
@@ -3585,13 +3585,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10742</v>
+        <v>11100</v>
       </c>
       <c r="C3" t="n">
-        <v>2801</v>
+        <v>2412</v>
       </c>
       <c r="D3" t="n">
-        <v>20335</v>
+        <v>16499</v>
       </c>
     </row>
     <row r="4">
@@ -3599,13 +3599,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>7068</v>
+        <v>7158</v>
       </c>
       <c r="C4" t="n">
-        <v>1526</v>
+        <v>1314</v>
       </c>
       <c r="D4" t="n">
-        <v>5610</v>
+        <v>5346</v>
       </c>
     </row>
     <row r="5">
@@ -3613,13 +3613,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4110</v>
+        <v>4053</v>
       </c>
       <c r="C5" t="n">
-        <v>534</v>
+        <v>480</v>
       </c>
       <c r="D5" t="n">
-        <v>1665</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="6">
@@ -3627,13 +3627,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2400</v>
+        <v>2433</v>
       </c>
       <c r="C6" t="n">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="D6" t="n">
-        <v>1289</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="7">
@@ -3641,13 +3641,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1076</v>
+        <v>1141</v>
       </c>
       <c r="C7" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D7" t="n">
-        <v>1012</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="8">
@@ -3655,13 +3655,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="C8" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D8" t="n">
-        <v>901</v>
+        <v>908</v>
       </c>
     </row>
     <row r="9">
@@ -3669,13 +3669,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D9" t="n">
-        <v>809</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10">
@@ -3683,13 +3683,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
         <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="11">
@@ -3700,10 +3700,10 @@
         <v>48</v>
       </c>
       <c r="C11" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D11" t="n">
-        <v>613</v>
+        <v>625</v>
       </c>
     </row>
     <row r="12">
@@ -3711,13 +3711,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>509</v>
+        <v>516</v>
       </c>
     </row>
     <row r="13">
@@ -3725,13 +3725,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14">
@@ -3739,13 +3739,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15">
@@ -3753,10 +3753,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>275</v>
@@ -3767,13 +3767,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17">
@@ -3781,13 +3781,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
@@ -3795,13 +3795,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
@@ -3809,13 +3809,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -3823,10 +3823,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -3882,13 +3882,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32455</v>
+        <v>33199</v>
       </c>
       <c r="C2" t="n">
-        <v>2554</v>
+        <v>2176</v>
       </c>
       <c r="D2" t="n">
-        <v>160308</v>
+        <v>121163</v>
       </c>
     </row>
     <row r="3">
@@ -3896,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14911</v>
+        <v>15688</v>
       </c>
       <c r="C3" t="n">
-        <v>2684</v>
+        <v>2307</v>
       </c>
       <c r="D3" t="n">
-        <v>24870</v>
+        <v>19858</v>
       </c>
     </row>
     <row r="4">
@@ -3910,13 +3910,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>8639</v>
+        <v>8766</v>
       </c>
       <c r="C4" t="n">
-        <v>1778</v>
+        <v>1518</v>
       </c>
       <c r="D4" t="n">
-        <v>6004</v>
+        <v>5611</v>
       </c>
     </row>
     <row r="5">
@@ -3924,13 +3924,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5522</v>
+        <v>5565</v>
       </c>
       <c r="C5" t="n">
-        <v>703</v>
+        <v>630</v>
       </c>
       <c r="D5" t="n">
-        <v>1727</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="6">
@@ -3938,13 +3938,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="C6" t="n">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="D6" t="n">
-        <v>1315</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="7">
@@ -3952,13 +3952,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1775</v>
+        <v>1859</v>
       </c>
       <c r="C7" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D7" t="n">
-        <v>1007</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="8">
@@ -3966,13 +3966,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>638</v>
+        <v>724</v>
       </c>
       <c r="C8" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D8" t="n">
-        <v>895</v>
+        <v>903</v>
       </c>
     </row>
     <row r="9">
@@ -3980,13 +3980,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="C9" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D9" t="n">
-        <v>802</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10">
@@ -3994,13 +3994,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>725</v>
+        <v>718</v>
       </c>
     </row>
     <row r="11">
@@ -4008,13 +4008,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D11" t="n">
-        <v>604</v>
+        <v>616</v>
       </c>
     </row>
     <row r="12">
@@ -4022,13 +4022,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>500</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13">
@@ -4036,13 +4036,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14">
@@ -4050,13 +4050,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15">
@@ -4064,13 +4064,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16">
@@ -4078,13 +4078,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17">
@@ -4092,13 +4092,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18">
@@ -4106,13 +4106,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
@@ -4120,13 +4120,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -4134,10 +4134,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>

--- a/4.1 Myrmidon Happy reef/output/yearly_population_growth_param_0.5.xlsx
+++ b/4.1 Myrmidon Happy reef/output/yearly_population_growth_param_0.5.xlsx
@@ -772,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43085</v>
+        <v>42277</v>
       </c>
       <c r="C2" t="n">
-        <v>2354</v>
+        <v>3769</v>
       </c>
       <c r="D2" t="n">
-        <v>108156</v>
+        <v>158598</v>
       </c>
     </row>
     <row r="3">
@@ -786,13 +786,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22998</v>
+        <v>22564</v>
       </c>
       <c r="C3" t="n">
-        <v>2115</v>
+        <v>2819</v>
       </c>
       <c r="D3" t="n">
-        <v>23147</v>
+        <v>31491</v>
       </c>
     </row>
     <row r="4">
@@ -800,13 +800,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11879</v>
+        <v>11515</v>
       </c>
       <c r="C4" t="n">
-        <v>1645</v>
+        <v>1900</v>
       </c>
       <c r="D4" t="n">
-        <v>5987</v>
+        <v>7038</v>
       </c>
     </row>
     <row r="5">
@@ -814,13 +814,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6929</v>
+        <v>6887</v>
       </c>
       <c r="C5" t="n">
-        <v>778</v>
+        <v>862</v>
       </c>
       <c r="D5" t="n">
-        <v>1771</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="6">
@@ -828,13 +828,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4525</v>
+        <v>4455</v>
       </c>
       <c r="C6" t="n">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="D6" t="n">
-        <v>1266</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="7">
@@ -842,13 +842,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2624</v>
+        <v>2594</v>
       </c>
       <c r="C7" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D7" t="n">
-        <v>1010</v>
+        <v>931</v>
       </c>
     </row>
     <row r="8">
@@ -856,13 +856,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1272</v>
+        <v>1335</v>
       </c>
       <c r="C8" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D8" t="n">
-        <v>898</v>
+        <v>822</v>
       </c>
     </row>
     <row r="9">
@@ -870,13 +870,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>419</v>
+        <v>522</v>
       </c>
       <c r="C9" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D9" t="n">
-        <v>816</v>
+        <v>754</v>
       </c>
     </row>
     <row r="10">
@@ -884,13 +884,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="C10" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>707</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11">
@@ -898,13 +898,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D11" t="n">
-        <v>607</v>
+        <v>599</v>
       </c>
     </row>
     <row r="12">
@@ -912,13 +912,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>498</v>
+        <v>512</v>
       </c>
     </row>
     <row r="13">
@@ -926,13 +926,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D13" t="n">
-        <v>408</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14">
@@ -943,10 +943,10 @@
         <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>323</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15">
@@ -954,13 +954,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>240</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16">
@@ -971,10 +971,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D16" t="n">
-        <v>152</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17">
@@ -982,13 +982,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18">
@@ -996,13 +996,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>28</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19">
@@ -1010,13 +1010,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20">
@@ -1024,13 +1024,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
@@ -1038,13 +1038,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1083,13 +1083,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>57810</v>
+        <v>54532</v>
       </c>
       <c r="C2" t="n">
-        <v>2130</v>
+        <v>3633</v>
       </c>
       <c r="D2" t="n">
-        <v>90954</v>
+        <v>134191</v>
       </c>
     </row>
     <row r="3">
@@ -1097,13 +1097,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29904</v>
+        <v>27982</v>
       </c>
       <c r="C3" t="n">
-        <v>2021</v>
+        <v>2761</v>
       </c>
       <c r="D3" t="n">
-        <v>25658</v>
+        <v>35366</v>
       </c>
     </row>
     <row r="4">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16771</v>
+        <v>15557</v>
       </c>
       <c r="C4" t="n">
-        <v>1680</v>
+        <v>1982</v>
       </c>
       <c r="D4" t="n">
-        <v>6463</v>
+        <v>7695</v>
       </c>
     </row>
     <row r="5">
@@ -1125,13 +1125,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9038</v>
+        <v>8461</v>
       </c>
       <c r="C5" t="n">
-        <v>911</v>
+        <v>1006</v>
       </c>
       <c r="D5" t="n">
-        <v>1855</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="6">
@@ -1139,13 +1139,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5681</v>
+        <v>5419</v>
       </c>
       <c r="C6" t="n">
-        <v>363</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>1277</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="7">
@@ -1153,13 +1153,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3505</v>
+        <v>3418</v>
       </c>
       <c r="C7" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="D7" t="n">
-        <v>1005</v>
+        <v>923</v>
       </c>
     </row>
     <row r="8">
@@ -1167,13 +1167,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1883</v>
+        <v>1908</v>
       </c>
       <c r="C8" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D8" t="n">
-        <v>892</v>
+        <v>809</v>
       </c>
     </row>
     <row r="9">
@@ -1181,13 +1181,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>773</v>
+        <v>907</v>
       </c>
       <c r="C9" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D9" t="n">
-        <v>807</v>
+        <v>741</v>
       </c>
     </row>
     <row r="10">
@@ -1195,13 +1195,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>219</v>
+        <v>314</v>
       </c>
       <c r="C10" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>702</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11">
@@ -1209,13 +1209,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C11" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="12">
@@ -1223,13 +1223,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>488</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13">
@@ -1237,13 +1237,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D13" t="n">
-        <v>396</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14">
@@ -1254,10 +1254,10 @@
         <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>310</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15">
@@ -1265,13 +1265,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>219</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16">
@@ -1282,10 +1282,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>133</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17">
@@ -1293,13 +1293,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18">
@@ -1307,13 +1307,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19">
@@ -1321,13 +1321,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -1335,13 +1335,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
@@ -1349,13 +1349,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1394,13 +1394,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>72150</v>
+        <v>65431</v>
       </c>
       <c r="C2" t="n">
-        <v>1573</v>
+        <v>2799</v>
       </c>
       <c r="D2" t="n">
-        <v>107106</v>
+        <v>162140</v>
       </c>
     </row>
     <row r="3">
@@ -1408,13 +1408,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>39280</v>
+        <v>34920</v>
       </c>
       <c r="C3" t="n">
-        <v>1914</v>
+        <v>2694</v>
       </c>
       <c r="D3" t="n">
-        <v>26803</v>
+        <v>36887</v>
       </c>
     </row>
     <row r="4">
@@ -1422,13 +1422,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21654</v>
+        <v>19315</v>
       </c>
       <c r="C4" t="n">
-        <v>1703</v>
+        <v>2029</v>
       </c>
       <c r="D4" t="n">
-        <v>6819</v>
+        <v>8449</v>
       </c>
     </row>
     <row r="5">
@@ -1436,13 +1436,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12104</v>
+        <v>10886</v>
       </c>
       <c r="C5" t="n">
-        <v>1001</v>
+        <v>1134</v>
       </c>
       <c r="D5" t="n">
-        <v>1899</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="6">
@@ -1450,13 +1450,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7196</v>
+        <v>6575</v>
       </c>
       <c r="C6" t="n">
-        <v>440</v>
+        <v>492</v>
       </c>
       <c r="D6" t="n">
-        <v>1276</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="7">
@@ -1464,13 +1464,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4413</v>
+        <v>4138</v>
       </c>
       <c r="C7" t="n">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="D7" t="n">
-        <v>1000</v>
+        <v>916</v>
       </c>
     </row>
     <row r="8">
@@ -1478,13 +1478,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2546</v>
+        <v>2520</v>
       </c>
       <c r="C8" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>886</v>
+        <v>797</v>
       </c>
     </row>
     <row r="9">
@@ -1492,13 +1492,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1183</v>
+        <v>1327</v>
       </c>
       <c r="C9" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D9" t="n">
-        <v>798</v>
+        <v>728</v>
       </c>
     </row>
     <row r="10">
@@ -1506,13 +1506,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>412</v>
+        <v>572</v>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>696</v>
+        <v>646</v>
       </c>
     </row>
     <row r="11">
@@ -1520,13 +1520,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="C11" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="12">
@@ -1534,13 +1534,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C12" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>473</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13">
@@ -1548,13 +1548,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D13" t="n">
-        <v>383</v>
+        <v>430</v>
       </c>
     </row>
     <row r="14">
@@ -1562,13 +1562,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>295</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15">
@@ -1576,13 +1576,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>199</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16">
@@ -1593,10 +1593,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>114</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17">
@@ -1607,10 +1607,10 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>48</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18">
@@ -1618,13 +1618,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19">
@@ -1632,13 +1632,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20">
@@ -1646,13 +1646,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -1660,13 +1660,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1705,13 +1705,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3679</v>
+        <v>3779</v>
       </c>
       <c r="C2" t="n">
-        <v>3661</v>
+        <v>4379</v>
       </c>
       <c r="D2" t="n">
-        <v>13429</v>
+        <v>16404</v>
       </c>
     </row>
     <row r="3">
@@ -1719,13 +1719,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>6300</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="4">
@@ -1733,13 +1733,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D4" t="n">
-        <v>5056</v>
+        <v>5035</v>
       </c>
     </row>
     <row r="5">
@@ -1747,13 +1747,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C5" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D5" t="n">
-        <v>1306</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="6">
@@ -1761,13 +1761,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D6" t="n">
-        <v>1137</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7">
@@ -1775,13 +1775,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" t="n">
-        <v>1043</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="8">
@@ -1789,13 +1789,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>938</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9">
@@ -1803,13 +1803,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" t="n">
-        <v>863</v>
+        <v>850</v>
       </c>
     </row>
     <row r="10">
@@ -1820,10 +1820,10 @@
         <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="11">
@@ -1837,7 +1837,7 @@
         <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="12">
@@ -1848,7 +1848,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
         <v>569</v>
@@ -1862,10 +1862,10 @@
         <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="14">
@@ -1873,13 +1873,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15">
@@ -1887,13 +1887,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="16">
@@ -1904,10 +1904,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>294</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17">
@@ -1915,13 +1915,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18">
@@ -1929,13 +1929,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19">
@@ -1946,10 +1946,10 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20">
@@ -1960,10 +1960,10 @@
         <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -1971,13 +1971,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2016,13 +2016,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5450</v>
+        <v>5922</v>
       </c>
       <c r="C2" t="n">
-        <v>4107</v>
+        <v>4987</v>
       </c>
       <c r="D2" t="n">
-        <v>46794</v>
+        <v>61361</v>
       </c>
     </row>
     <row r="3">
@@ -2030,13 +2030,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2357</v>
+        <v>2391</v>
       </c>
       <c r="C3" t="n">
-        <v>804</v>
+        <v>939</v>
       </c>
       <c r="D3" t="n">
-        <v>6282</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="4">
@@ -2044,13 +2044,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D4" t="n">
-        <v>5010</v>
+        <v>4901</v>
       </c>
     </row>
     <row r="5">
@@ -2058,13 +2058,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C5" t="n">
         <v>126</v>
       </c>
       <c r="D5" t="n">
-        <v>1374</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="6">
@@ -2072,13 +2072,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C6" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D6" t="n">
-        <v>1149</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="7">
@@ -2086,13 +2086,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D7" t="n">
-        <v>1039</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="8">
@@ -2100,13 +2100,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>933</v>
+        <v>914</v>
       </c>
     </row>
     <row r="9">
@@ -2114,13 +2114,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D9" t="n">
-        <v>854</v>
+        <v>836</v>
       </c>
     </row>
     <row r="10">
@@ -2128,13 +2128,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>750</v>
+        <v>738</v>
       </c>
     </row>
     <row r="11">
@@ -2145,10 +2145,10 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>666</v>
+        <v>660</v>
       </c>
     </row>
     <row r="12">
@@ -2159,10 +2159,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="13">
@@ -2170,13 +2170,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>477</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14">
@@ -2184,13 +2184,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15">
@@ -2198,13 +2198,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16">
@@ -2212,13 +2212,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>276</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17">
@@ -2226,13 +2226,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>209</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18">
@@ -2240,13 +2240,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19">
@@ -2257,10 +2257,10 @@
         <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D19" t="n">
-        <v>85</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20">
@@ -2268,13 +2268,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -2282,13 +2282,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2327,13 +2327,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6107</v>
+        <v>7066</v>
       </c>
       <c r="C2" t="n">
-        <v>3585</v>
+        <v>4410</v>
       </c>
       <c r="D2" t="n">
-        <v>51363</v>
+        <v>67820</v>
       </c>
     </row>
     <row r="3">
@@ -2341,13 +2341,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3909</v>
+        <v>4143</v>
       </c>
       <c r="C3" t="n">
-        <v>1382</v>
+        <v>1642</v>
       </c>
       <c r="D3" t="n">
-        <v>7600</v>
+        <v>8714</v>
       </c>
     </row>
     <row r="4">
@@ -2355,13 +2355,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="C4" t="n">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="D4" t="n">
-        <v>4966</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="5">
@@ -2369,13 +2369,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D5" t="n">
-        <v>1436</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="6">
@@ -2383,13 +2383,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D6" t="n">
-        <v>1162</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="7">
@@ -2397,13 +2397,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C7" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D7" t="n">
-        <v>1035</v>
+        <v>998</v>
       </c>
     </row>
     <row r="8">
@@ -2411,13 +2411,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D8" t="n">
-        <v>928</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9">
@@ -2425,13 +2425,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D9" t="n">
-        <v>846</v>
+        <v>823</v>
       </c>
     </row>
     <row r="10">
@@ -2439,13 +2439,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>748</v>
+        <v>728</v>
       </c>
     </row>
     <row r="11">
@@ -2453,13 +2453,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>658</v>
+        <v>650</v>
       </c>
     </row>
     <row r="12">
@@ -2467,13 +2467,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="13">
@@ -2481,13 +2481,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>467</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14">
@@ -2498,10 +2498,10 @@
         <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15">
@@ -2509,13 +2509,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>337</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16">
@@ -2523,13 +2523,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>259</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17">
@@ -2537,13 +2537,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>194</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18">
@@ -2554,10 +2554,10 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>130</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19">
@@ -2565,13 +2565,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20">
@@ -2582,10 +2582,10 @@
         <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -2593,13 +2593,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2638,13 +2638,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8905</v>
+        <v>10680</v>
       </c>
       <c r="C2" t="n">
-        <v>4795</v>
+        <v>6142</v>
       </c>
       <c r="D2" t="n">
-        <v>82786</v>
+        <v>112329</v>
       </c>
     </row>
     <row r="3">
@@ -2652,13 +2652,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4656</v>
+        <v>5164</v>
       </c>
       <c r="C3" t="n">
-        <v>1709</v>
+        <v>2025</v>
       </c>
       <c r="D3" t="n">
-        <v>8985</v>
+        <v>11118</v>
       </c>
     </row>
     <row r="4">
@@ -2666,13 +2666,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2956</v>
+        <v>3043</v>
       </c>
       <c r="C4" t="n">
-        <v>535</v>
+        <v>610</v>
       </c>
       <c r="D4" t="n">
-        <v>4989</v>
+        <v>4824</v>
       </c>
     </row>
     <row r="5">
@@ -2680,13 +2680,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C5" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D5" t="n">
-        <v>1494</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="6">
@@ -2694,13 +2694,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D6" t="n">
-        <v>1176</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="7">
@@ -2708,13 +2708,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C7" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D7" t="n">
-        <v>1031</v>
+        <v>984</v>
       </c>
     </row>
     <row r="8">
@@ -2722,13 +2722,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D8" t="n">
-        <v>923</v>
+        <v>886</v>
       </c>
     </row>
     <row r="9">
@@ -2736,13 +2736,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D9" t="n">
-        <v>838</v>
+        <v>810</v>
       </c>
     </row>
     <row r="10">
@@ -2750,13 +2750,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>746</v>
+        <v>718</v>
       </c>
     </row>
     <row r="11">
@@ -2764,13 +2764,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>650</v>
+        <v>640</v>
       </c>
     </row>
     <row r="12">
@@ -2781,10 +2781,10 @@
         <v>36</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>540</v>
+        <v>548</v>
       </c>
     </row>
     <row r="13">
@@ -2792,13 +2792,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>462</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14">
@@ -2806,13 +2806,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>386</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15">
@@ -2820,13 +2820,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>323</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16">
@@ -2834,13 +2834,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>242</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17">
@@ -2848,13 +2848,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>177</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18">
@@ -2862,13 +2862,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>107</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19">
@@ -2879,10 +2879,10 @@
         <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20">
@@ -2890,13 +2890,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -2904,13 +2904,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2949,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12320</v>
+        <v>14473</v>
       </c>
       <c r="C2" t="n">
-        <v>3910</v>
+        <v>5131</v>
       </c>
       <c r="D2" t="n">
-        <v>81758</v>
+        <v>111486</v>
       </c>
     </row>
     <row r="3">
@@ -2963,13 +2963,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6532</v>
+        <v>7593</v>
       </c>
       <c r="C3" t="n">
-        <v>2183</v>
+        <v>2627</v>
       </c>
       <c r="D3" t="n">
-        <v>11505</v>
+        <v>15424</v>
       </c>
     </row>
     <row r="4">
@@ -2977,13 +2977,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3763</v>
+        <v>3947</v>
       </c>
       <c r="C4" t="n">
-        <v>783</v>
+        <v>903</v>
       </c>
       <c r="D4" t="n">
-        <v>5077</v>
+        <v>5039</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2167</v>
+        <v>2193</v>
       </c>
       <c r="C5" t="n">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="D5" t="n">
-        <v>1549</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="6">
@@ -3005,13 +3005,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>692</v>
+        <v>716</v>
       </c>
       <c r="C6" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D6" t="n">
-        <v>1191</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="7">
@@ -3019,13 +3019,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C7" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D7" t="n">
-        <v>1027</v>
+        <v>971</v>
       </c>
     </row>
     <row r="8">
@@ -3033,13 +3033,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>918</v>
+        <v>873</v>
       </c>
     </row>
     <row r="9">
@@ -3047,13 +3047,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D9" t="n">
-        <v>831</v>
+        <v>797</v>
       </c>
     </row>
     <row r="10">
@@ -3061,13 +3061,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>743</v>
+        <v>708</v>
       </c>
     </row>
     <row r="11">
@@ -3075,13 +3075,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D11" t="n">
-        <v>642</v>
+        <v>631</v>
       </c>
     </row>
     <row r="12">
@@ -3089,13 +3089,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>532</v>
+        <v>541</v>
       </c>
     </row>
     <row r="13">
@@ -3103,13 +3103,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>452</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14">
@@ -3117,13 +3117,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>376</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15">
@@ -3134,10 +3134,10 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>308</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16">
@@ -3145,13 +3145,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>225</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17">
@@ -3159,13 +3159,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>157</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18">
@@ -3173,13 +3173,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>86</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19">
@@ -3190,10 +3190,10 @@
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20">
@@ -3201,13 +3201,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -3215,13 +3215,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3260,13 +3260,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14928</v>
+        <v>16646</v>
       </c>
       <c r="C2" t="n">
-        <v>3493</v>
+        <v>4794</v>
       </c>
       <c r="D2" t="n">
-        <v>92847</v>
+        <v>129635</v>
       </c>
     </row>
     <row r="3">
@@ -3274,13 +3274,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9109</v>
+        <v>10250</v>
       </c>
       <c r="C3" t="n">
-        <v>2364</v>
+        <v>2870</v>
       </c>
       <c r="D3" t="n">
-        <v>13873</v>
+        <v>18526</v>
       </c>
     </row>
     <row r="4">
@@ -3288,13 +3288,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5142</v>
+        <v>5695</v>
       </c>
       <c r="C4" t="n">
-        <v>1075</v>
+        <v>1230</v>
       </c>
       <c r="D4" t="n">
-        <v>5169</v>
+        <v>5335</v>
       </c>
     </row>
     <row r="5">
@@ -3302,13 +3302,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2985</v>
+        <v>3022</v>
       </c>
       <c r="C5" t="n">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="D5" t="n">
-        <v>1603</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="6">
@@ -3316,13 +3316,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1639</v>
+        <v>1650</v>
       </c>
       <c r="C6" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D6" t="n">
-        <v>1206</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="7">
@@ -3330,13 +3330,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>437</v>
+        <v>478</v>
       </c>
       <c r="C7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D7" t="n">
-        <v>1023</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
@@ -3344,13 +3344,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C8" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>913</v>
+        <v>860</v>
       </c>
     </row>
     <row r="9">
@@ -3358,13 +3358,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D9" t="n">
-        <v>824</v>
+        <v>784</v>
       </c>
     </row>
     <row r="10">
@@ -3372,13 +3372,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>740</v>
+        <v>698</v>
       </c>
     </row>
     <row r="11">
@@ -3386,13 +3386,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D11" t="n">
-        <v>634</v>
+        <v>622</v>
       </c>
     </row>
     <row r="12">
@@ -3400,13 +3400,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>524</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13">
@@ -3417,10 +3417,10 @@
         <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>442</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14">
@@ -3428,13 +3428,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>364</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15">
@@ -3442,13 +3442,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>292</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16">
@@ -3456,13 +3456,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>207</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17">
@@ -3470,13 +3470,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>137</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18">
@@ -3484,13 +3484,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19">
@@ -3498,13 +3498,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20">
@@ -3512,13 +3512,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -3526,13 +3526,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3571,13 +3571,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21759</v>
+        <v>23145</v>
       </c>
       <c r="C2" t="n">
-        <v>2850</v>
+        <v>4054</v>
       </c>
       <c r="D2" t="n">
-        <v>116330</v>
+        <v>166621</v>
       </c>
     </row>
     <row r="3">
@@ -3585,13 +3585,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11100</v>
+        <v>11987</v>
       </c>
       <c r="C3" t="n">
-        <v>2412</v>
+        <v>3020</v>
       </c>
       <c r="D3" t="n">
-        <v>16499</v>
+        <v>22081</v>
       </c>
     </row>
     <row r="4">
@@ -3599,13 +3599,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>7158</v>
+        <v>7656</v>
       </c>
       <c r="C4" t="n">
-        <v>1314</v>
+        <v>1511</v>
       </c>
       <c r="D4" t="n">
-        <v>5346</v>
+        <v>5754</v>
       </c>
     </row>
     <row r="5">
@@ -3613,13 +3613,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4053</v>
+        <v>4262</v>
       </c>
       <c r="C5" t="n">
-        <v>480</v>
+        <v>536</v>
       </c>
       <c r="D5" t="n">
-        <v>1656</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="6">
@@ -3627,13 +3627,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2433</v>
+        <v>2399</v>
       </c>
       <c r="C6" t="n">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D6" t="n">
-        <v>1222</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="7">
@@ -3641,13 +3641,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1141</v>
+        <v>1193</v>
       </c>
       <c r="C7" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D7" t="n">
-        <v>1019</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8">
@@ -3655,13 +3655,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>266</v>
+        <v>311</v>
       </c>
       <c r="C8" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>908</v>
+        <v>847</v>
       </c>
     </row>
     <row r="9">
@@ -3669,13 +3669,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D9" t="n">
-        <v>825</v>
+        <v>772</v>
       </c>
     </row>
     <row r="10">
@@ -3683,13 +3683,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>729</v>
+        <v>688</v>
       </c>
     </row>
     <row r="11">
@@ -3697,13 +3697,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D11" t="n">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="12">
@@ -3711,13 +3711,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C12" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>516</v>
+        <v>526</v>
       </c>
     </row>
     <row r="13">
@@ -3725,13 +3725,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D13" t="n">
-        <v>431</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14">
@@ -3739,13 +3739,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>351</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15">
@@ -3753,13 +3753,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>275</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16">
@@ -3770,10 +3770,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>189</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17">
@@ -3781,13 +3781,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18">
@@ -3795,13 +3795,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19">
@@ -3809,13 +3809,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20">
@@ -3823,13 +3823,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -3837,13 +3837,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3882,13 +3882,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33199</v>
+        <v>34570</v>
       </c>
       <c r="C2" t="n">
-        <v>2176</v>
+        <v>3204</v>
       </c>
       <c r="D2" t="n">
-        <v>121163</v>
+        <v>176194</v>
       </c>
     </row>
     <row r="3">
@@ -3896,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15688</v>
+        <v>15859</v>
       </c>
       <c r="C3" t="n">
-        <v>2307</v>
+        <v>3000</v>
       </c>
       <c r="D3" t="n">
-        <v>19858</v>
+        <v>26802</v>
       </c>
     </row>
     <row r="4">
@@ -3910,13 +3910,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>8766</v>
+        <v>9097</v>
       </c>
       <c r="C4" t="n">
-        <v>1518</v>
+        <v>1740</v>
       </c>
       <c r="D4" t="n">
-        <v>5611</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="5">
@@ -3924,13 +3924,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5565</v>
+        <v>5709</v>
       </c>
       <c r="C5" t="n">
-        <v>630</v>
+        <v>701</v>
       </c>
       <c r="D5" t="n">
-        <v>1711</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="6">
@@ -3938,13 +3938,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3340</v>
+        <v>3374</v>
       </c>
       <c r="C6" t="n">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="D6" t="n">
-        <v>1239</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="7">
@@ -3952,13 +3952,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1859</v>
+        <v>1837</v>
       </c>
       <c r="C7" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D7" t="n">
-        <v>1015</v>
+        <v>941</v>
       </c>
     </row>
     <row r="8">
@@ -3966,13 +3966,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>724</v>
+        <v>811</v>
       </c>
       <c r="C8" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
-        <v>903</v>
+        <v>835</v>
       </c>
     </row>
     <row r="9">
@@ -3980,13 +3980,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D9" t="n">
-        <v>825</v>
+        <v>767</v>
       </c>
     </row>
     <row r="10">
@@ -3994,13 +3994,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>718</v>
+        <v>677</v>
       </c>
     </row>
     <row r="11">
@@ -4008,13 +4008,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D11" t="n">
-        <v>616</v>
+        <v>609</v>
       </c>
     </row>
     <row r="12">
@@ -4022,13 +4022,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C12" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>507</v>
+        <v>519</v>
       </c>
     </row>
     <row r="13">
@@ -4036,13 +4036,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D13" t="n">
-        <v>420</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14">
@@ -4050,13 +4050,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>337</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15">
@@ -4064,13 +4064,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>258</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16">
@@ -4081,10 +4081,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>171</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17">
@@ -4092,13 +4092,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>96</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18">
@@ -4109,10 +4109,10 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19">
@@ -4120,13 +4120,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20">
@@ -4134,13 +4134,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21">
@@ -4148,13 +4148,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/4.1 Myrmidon Happy reef/output/yearly_population_growth_param_0.5.xlsx
+++ b/4.1 Myrmidon Happy reef/output/yearly_population_growth_param_0.5.xlsx
@@ -772,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42277</v>
+        <v>42848</v>
       </c>
       <c r="C2" t="n">
-        <v>3769</v>
+        <v>4403</v>
       </c>
       <c r="D2" t="n">
-        <v>158598</v>
+        <v>152592</v>
       </c>
     </row>
     <row r="3">
@@ -786,13 +786,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22564</v>
+        <v>23031</v>
       </c>
       <c r="C3" t="n">
-        <v>2819</v>
+        <v>3359</v>
       </c>
       <c r="D3" t="n">
-        <v>31491</v>
+        <v>30456</v>
       </c>
     </row>
     <row r="4">
@@ -800,13 +800,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11515</v>
+        <v>11681</v>
       </c>
       <c r="C4" t="n">
-        <v>1900</v>
+        <v>2376</v>
       </c>
       <c r="D4" t="n">
-        <v>7038</v>
+        <v>6951</v>
       </c>
     </row>
     <row r="5">
@@ -814,13 +814,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6887</v>
+        <v>7105</v>
       </c>
       <c r="C5" t="n">
-        <v>862</v>
+        <v>1071</v>
       </c>
       <c r="D5" t="n">
-        <v>2255</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="6">
@@ -828,13 +828,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4455</v>
+        <v>4689</v>
       </c>
       <c r="C6" t="n">
-        <v>323</v>
+        <v>372</v>
       </c>
       <c r="D6" t="n">
-        <v>1217</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="7">
@@ -842,13 +842,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2594</v>
+        <v>2634</v>
       </c>
       <c r="C7" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D7" t="n">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="8">
@@ -856,13 +856,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1335</v>
+        <v>1279</v>
       </c>
       <c r="C8" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D8" t="n">
-        <v>822</v>
+        <v>826</v>
       </c>
     </row>
     <row r="9">
@@ -870,13 +870,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>522</v>
+        <v>442</v>
       </c>
       <c r="C9" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D9" t="n">
-        <v>754</v>
+        <v>773</v>
       </c>
     </row>
     <row r="10">
@@ -884,10 +884,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
         <v>666</v>
@@ -898,13 +898,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>599</v>
+        <v>594</v>
       </c>
     </row>
     <row r="12">
@@ -912,13 +912,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="13">
@@ -929,10 +929,10 @@
         <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14">
@@ -940,13 +940,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15">
@@ -954,13 +954,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16">
@@ -968,13 +968,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>28</v>
       </c>
       <c r="D16" t="n">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17">
@@ -982,13 +982,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18">
@@ -996,13 +996,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
         <v>28</v>
       </c>
       <c r="D18" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19">
@@ -1010,13 +1010,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
@@ -1030,7 +1030,7 @@
         <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
@@ -1038,13 +1038,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1083,13 +1083,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>54532</v>
+        <v>55820</v>
       </c>
       <c r="C2" t="n">
-        <v>3633</v>
+        <v>4193</v>
       </c>
       <c r="D2" t="n">
-        <v>134191</v>
+        <v>129095</v>
       </c>
     </row>
     <row r="3">
@@ -1097,13 +1097,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27982</v>
+        <v>28562</v>
       </c>
       <c r="C3" t="n">
-        <v>2761</v>
+        <v>3313</v>
       </c>
       <c r="D3" t="n">
-        <v>35366</v>
+        <v>33879</v>
       </c>
     </row>
     <row r="4">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15557</v>
+        <v>16050</v>
       </c>
       <c r="C4" t="n">
-        <v>1982</v>
+        <v>2450</v>
       </c>
       <c r="D4" t="n">
-        <v>7695</v>
+        <v>7867</v>
       </c>
     </row>
     <row r="5">
@@ -1125,13 +1125,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>8461</v>
+        <v>8694</v>
       </c>
       <c r="C5" t="n">
-        <v>1006</v>
+        <v>1263</v>
       </c>
       <c r="D5" t="n">
-        <v>2348</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="6">
@@ -1139,13 +1139,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5419</v>
+        <v>5691</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>481</v>
       </c>
       <c r="D6" t="n">
-        <v>1231</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="7">
@@ -1153,13 +1153,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3418</v>
+        <v>3526</v>
       </c>
       <c r="C7" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D7" t="n">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="8">
@@ -1167,13 +1167,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1908</v>
+        <v>1880</v>
       </c>
       <c r="C8" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D8" t="n">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
     <row r="9">
@@ -1181,13 +1181,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>907</v>
+        <v>803</v>
       </c>
       <c r="C9" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D9" t="n">
-        <v>741</v>
+        <v>767</v>
       </c>
     </row>
     <row r="10">
@@ -1195,13 +1195,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>314</v>
+        <v>243</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="11">
@@ -1209,13 +1209,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C11" t="n">
         <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12">
@@ -1223,13 +1223,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="13">
@@ -1237,13 +1237,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14">
@@ -1251,13 +1251,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15">
@@ -1265,13 +1265,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>324</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16">
@@ -1279,13 +1279,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17">
@@ -1293,13 +1293,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>27</v>
       </c>
       <c r="D17" t="n">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18">
@@ -1307,7 +1307,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
         <v>27</v>
@@ -1321,13 +1321,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
         <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20">
@@ -1335,13 +1335,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
         <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
@@ -1349,13 +1349,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1394,13 +1394,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>65431</v>
+        <v>67176</v>
       </c>
       <c r="C2" t="n">
-        <v>2799</v>
+        <v>3228</v>
       </c>
       <c r="D2" t="n">
-        <v>162140</v>
+        <v>156003</v>
       </c>
     </row>
     <row r="3">
@@ -1408,13 +1408,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>34920</v>
+        <v>35917</v>
       </c>
       <c r="C3" t="n">
-        <v>2694</v>
+        <v>3210</v>
       </c>
       <c r="D3" t="n">
-        <v>36887</v>
+        <v>35353</v>
       </c>
     </row>
     <row r="4">
@@ -1422,13 +1422,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19315</v>
+        <v>20024</v>
       </c>
       <c r="C4" t="n">
-        <v>2029</v>
+        <v>2492</v>
       </c>
       <c r="D4" t="n">
-        <v>8449</v>
+        <v>8551</v>
       </c>
     </row>
     <row r="5">
@@ -1436,13 +1436,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10886</v>
+        <v>11296</v>
       </c>
       <c r="C5" t="n">
-        <v>1134</v>
+        <v>1418</v>
       </c>
       <c r="D5" t="n">
-        <v>2459</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="6">
@@ -1450,13 +1450,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6575</v>
+        <v>6834</v>
       </c>
       <c r="C6" t="n">
-        <v>492</v>
+        <v>594</v>
       </c>
       <c r="D6" t="n">
-        <v>1248</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="7">
@@ -1464,13 +1464,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4138</v>
+        <v>4343</v>
       </c>
       <c r="C7" t="n">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="D7" t="n">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="8">
@@ -1478,13 +1478,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2520</v>
+        <v>2517</v>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D8" t="n">
-        <v>797</v>
+        <v>808</v>
       </c>
     </row>
     <row r="9">
@@ -1492,13 +1492,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1327</v>
+        <v>1224</v>
       </c>
       <c r="C9" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D9" t="n">
-        <v>728</v>
+        <v>753</v>
       </c>
     </row>
     <row r="10">
@@ -1506,13 +1506,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>572</v>
+        <v>461</v>
       </c>
       <c r="C10" t="n">
         <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="11">
@@ -1520,13 +1520,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="C11" t="n">
         <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="12">
@@ -1534,13 +1534,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" t="n">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13">
@@ -1548,13 +1548,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14">
@@ -1565,10 +1565,10 @@
         <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15">
@@ -1576,13 +1576,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>318</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16">
@@ -1590,13 +1590,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17">
@@ -1604,13 +1604,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18">
@@ -1618,13 +1618,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19">
@@ -1632,13 +1632,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20">
@@ -1646,13 +1646,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21">
@@ -1660,13 +1660,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1705,13 +1705,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3779</v>
+        <v>3915</v>
       </c>
       <c r="C2" t="n">
-        <v>4379</v>
+        <v>5356</v>
       </c>
       <c r="D2" t="n">
-        <v>16404</v>
+        <v>15973</v>
       </c>
     </row>
     <row r="3">
@@ -1733,10 +1733,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D4" t="n">
         <v>5035</v>
@@ -1750,10 +1750,10 @@
         <v>75</v>
       </c>
       <c r="C5" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" t="n">
-        <v>1407</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="6">
@@ -1761,13 +1761,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" t="n">
-        <v>1118</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="7">
@@ -1775,10 +1775,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D7" t="n">
         <v>1030</v>
@@ -1792,7 +1792,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" t="n">
         <v>928</v>
@@ -1806,10 +1806,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D9" t="n">
-        <v>850</v>
+        <v>858</v>
       </c>
     </row>
     <row r="10">
@@ -1820,10 +1820,10 @@
         <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="11">
@@ -1851,7 +1851,7 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="13">
@@ -1865,7 +1865,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14">
@@ -1879,7 +1879,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15">
@@ -1893,7 +1893,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16">
@@ -1907,7 +1907,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17">
@@ -1935,7 +1935,7 @@
         <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19">
@@ -1949,7 +1949,7 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20">
@@ -1963,7 +1963,7 @@
         <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
@@ -1971,13 +1971,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2016,13 +2016,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5922</v>
+        <v>6052</v>
       </c>
       <c r="C2" t="n">
-        <v>4987</v>
+        <v>6090</v>
       </c>
       <c r="D2" t="n">
-        <v>61361</v>
+        <v>59337</v>
       </c>
     </row>
     <row r="3">
@@ -2030,13 +2030,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2391</v>
+        <v>2477</v>
       </c>
       <c r="C3" t="n">
-        <v>939</v>
+        <v>1127</v>
       </c>
       <c r="D3" t="n">
-        <v>6393</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="4">
@@ -2044,10 +2044,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D4" t="n">
         <v>4901</v>
@@ -2058,13 +2058,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D5" t="n">
-        <v>1559</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="6">
@@ -2072,13 +2072,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D6" t="n">
-        <v>1121</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="7">
@@ -2086,10 +2086,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D7" t="n">
         <v>1013</v>
@@ -2100,10 +2100,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" t="n">
         <v>914</v>
@@ -2117,10 +2117,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D9" t="n">
-        <v>836</v>
+        <v>852</v>
       </c>
     </row>
     <row r="10">
@@ -2131,10 +2131,10 @@
         <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11">
@@ -2148,7 +2148,7 @@
         <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="12">
@@ -2162,7 +2162,7 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="13">
@@ -2170,13 +2170,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
         <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="14">
@@ -2187,10 +2187,10 @@
         <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15">
@@ -2204,7 +2204,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16">
@@ -2218,7 +2218,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17">
@@ -2226,13 +2226,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18">
@@ -2246,7 +2246,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19">
@@ -2260,7 +2260,7 @@
         <v>35</v>
       </c>
       <c r="D19" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20">
@@ -2274,7 +2274,7 @@
         <v>35</v>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
@@ -2282,13 +2282,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2327,13 +2327,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7066</v>
+        <v>7002</v>
       </c>
       <c r="C2" t="n">
-        <v>4410</v>
+        <v>5377</v>
       </c>
       <c r="D2" t="n">
-        <v>67820</v>
+        <v>65521</v>
       </c>
     </row>
     <row r="3">
@@ -2341,13 +2341,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4143</v>
+        <v>4289</v>
       </c>
       <c r="C3" t="n">
-        <v>1642</v>
+        <v>1991</v>
       </c>
       <c r="D3" t="n">
-        <v>8714</v>
+        <v>8598</v>
       </c>
     </row>
     <row r="4">
@@ -2355,13 +2355,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1593</v>
+        <v>1650</v>
       </c>
       <c r="C4" t="n">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="D4" t="n">
-        <v>4790</v>
+        <v>4789</v>
       </c>
     </row>
     <row r="5">
@@ -2369,13 +2369,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D5" t="n">
-        <v>1689</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="6">
@@ -2383,13 +2383,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C6" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D6" t="n">
-        <v>1133</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="7">
@@ -2397,13 +2397,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D7" t="n">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="8">
@@ -2411,7 +2411,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
         <v>77</v>
@@ -2425,13 +2425,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
         <v>69</v>
       </c>
       <c r="D9" t="n">
-        <v>823</v>
+        <v>846</v>
       </c>
     </row>
     <row r="10">
@@ -2439,13 +2439,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
         <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="11">
@@ -2453,13 +2453,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
         <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12">
@@ -2473,7 +2473,7 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="13">
@@ -2481,13 +2481,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14">
@@ -2495,13 +2495,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
         <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15">
@@ -2515,7 +2515,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16">
@@ -2529,7 +2529,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17">
@@ -2537,13 +2537,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18">
@@ -2551,13 +2551,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
@@ -2571,7 +2571,7 @@
         <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20">
@@ -2585,7 +2585,7 @@
         <v>34</v>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -2593,13 +2593,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2638,13 +2638,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10680</v>
+        <v>10765</v>
       </c>
       <c r="C2" t="n">
-        <v>6142</v>
+        <v>7454</v>
       </c>
       <c r="D2" t="n">
-        <v>112329</v>
+        <v>108377</v>
       </c>
     </row>
     <row r="3">
@@ -2652,13 +2652,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5164</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="n">
-        <v>2025</v>
+        <v>2461</v>
       </c>
       <c r="D3" t="n">
-        <v>11118</v>
+        <v>10903</v>
       </c>
     </row>
     <row r="4">
@@ -2666,13 +2666,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3043</v>
+        <v>3201</v>
       </c>
       <c r="C4" t="n">
-        <v>610</v>
+        <v>720</v>
       </c>
       <c r="D4" t="n">
-        <v>4824</v>
+        <v>4862</v>
       </c>
     </row>
     <row r="5">
@@ -2680,13 +2680,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1037</v>
+        <v>1061</v>
       </c>
       <c r="C5" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D5" t="n">
-        <v>1816</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="6">
@@ -2694,13 +2694,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D6" t="n">
-        <v>1135</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="7">
@@ -2708,13 +2708,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C7" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D7" t="n">
-        <v>984</v>
+        <v>981</v>
       </c>
     </row>
     <row r="8">
@@ -2722,10 +2722,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
         <v>886</v>
@@ -2736,13 +2736,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" t="n">
-        <v>810</v>
+        <v>840</v>
       </c>
     </row>
     <row r="10">
@@ -2750,13 +2750,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="11">
@@ -2770,7 +2770,7 @@
         <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="12">
@@ -2778,13 +2778,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" t="n">
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13">
@@ -2792,13 +2792,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="14">
@@ -2806,13 +2806,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
         <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>399</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15">
@@ -2820,13 +2820,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
         <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16">
@@ -2840,7 +2840,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17">
@@ -2848,13 +2848,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18">
@@ -2862,13 +2862,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19">
@@ -2876,13 +2876,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
         <v>33</v>
       </c>
       <c r="D19" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
@@ -2896,7 +2896,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
@@ -2904,13 +2904,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2949,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14473</v>
+        <v>14675</v>
       </c>
       <c r="C2" t="n">
-        <v>5131</v>
+        <v>6218</v>
       </c>
       <c r="D2" t="n">
-        <v>111486</v>
+        <v>107511</v>
       </c>
     </row>
     <row r="3">
@@ -2963,13 +2963,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7593</v>
+        <v>7602</v>
       </c>
       <c r="C3" t="n">
-        <v>2627</v>
+        <v>3190</v>
       </c>
       <c r="D3" t="n">
-        <v>15424</v>
+        <v>15040</v>
       </c>
     </row>
     <row r="4">
@@ -2977,13 +2977,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3947</v>
+        <v>4085</v>
       </c>
       <c r="C4" t="n">
-        <v>903</v>
+        <v>1082</v>
       </c>
       <c r="D4" t="n">
-        <v>5039</v>
+        <v>5062</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2193</v>
+        <v>2275</v>
       </c>
       <c r="C5" t="n">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="D5" t="n">
-        <v>1887</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="6">
@@ -3005,13 +3005,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="C6" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D6" t="n">
-        <v>1143</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="7">
@@ -3019,13 +3019,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C7" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D7" t="n">
-        <v>971</v>
+        <v>967</v>
       </c>
     </row>
     <row r="8">
@@ -3033,13 +3033,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" t="n">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="9">
@@ -3047,13 +3047,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" t="n">
-        <v>797</v>
+        <v>833</v>
       </c>
     </row>
     <row r="10">
@@ -3061,13 +3061,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11">
@@ -3075,13 +3075,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12">
@@ -3095,7 +3095,7 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13">
@@ -3103,10 +3103,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
         <v>467</v>
@@ -3117,13 +3117,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
         <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15">
@@ -3131,13 +3131,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
         <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>346</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16">
@@ -3145,13 +3145,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17">
@@ -3165,7 +3165,7 @@
         <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18">
@@ -3173,13 +3173,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19">
@@ -3187,13 +3187,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
         <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
@@ -3201,13 +3201,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
         <v>32</v>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
@@ -3215,13 +3215,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3260,13 +3260,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16646</v>
+        <v>16315</v>
       </c>
       <c r="C2" t="n">
-        <v>4794</v>
+        <v>5737</v>
       </c>
       <c r="D2" t="n">
-        <v>129635</v>
+        <v>124923</v>
       </c>
     </row>
     <row r="3">
@@ -3274,13 +3274,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10250</v>
+        <v>10424</v>
       </c>
       <c r="C3" t="n">
-        <v>2870</v>
+        <v>3532</v>
       </c>
       <c r="D3" t="n">
-        <v>18526</v>
+        <v>18016</v>
       </c>
     </row>
     <row r="4">
@@ -3288,13 +3288,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5695</v>
+        <v>5832</v>
       </c>
       <c r="C4" t="n">
-        <v>1230</v>
+        <v>1483</v>
       </c>
       <c r="D4" t="n">
-        <v>5335</v>
+        <v>5338</v>
       </c>
     </row>
     <row r="5">
@@ -3302,13 +3302,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3022</v>
+        <v>3157</v>
       </c>
       <c r="C5" t="n">
-        <v>380</v>
+        <v>447</v>
       </c>
       <c r="D5" t="n">
-        <v>1962</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="6">
@@ -3316,13 +3316,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1650</v>
+        <v>1665</v>
       </c>
       <c r="C6" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D6" t="n">
-        <v>1154</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="7">
@@ -3330,13 +3330,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>478</v>
+        <v>450</v>
       </c>
       <c r="C7" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D7" t="n">
-        <v>960</v>
+        <v>954</v>
       </c>
     </row>
     <row r="8">
@@ -3344,13 +3344,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
-        <v>860</v>
+        <v>867</v>
       </c>
     </row>
     <row r="9">
@@ -3358,13 +3358,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" t="n">
-        <v>784</v>
+        <v>817</v>
       </c>
     </row>
     <row r="10">
@@ -3372,13 +3372,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="11">
@@ -3386,13 +3386,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>622</v>
+        <v>618</v>
       </c>
     </row>
     <row r="12">
@@ -3400,13 +3400,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
     <row r="13">
@@ -3417,10 +3417,10 @@
         <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="14">
@@ -3428,13 +3428,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" t="n">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15">
@@ -3442,13 +3442,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>341</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16">
@@ -3456,13 +3456,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17">
@@ -3476,7 +3476,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18">
@@ -3490,7 +3490,7 @@
         <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19">
@@ -3498,13 +3498,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20">
@@ -3512,13 +3512,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
         <v>31</v>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
@@ -3526,13 +3526,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3571,13 +3571,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23145</v>
+        <v>22969</v>
       </c>
       <c r="C2" t="n">
-        <v>4054</v>
+        <v>4831</v>
       </c>
       <c r="D2" t="n">
-        <v>166621</v>
+        <v>160427</v>
       </c>
     </row>
     <row r="3">
@@ -3585,13 +3585,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11987</v>
+        <v>11884</v>
       </c>
       <c r="C3" t="n">
-        <v>3020</v>
+        <v>3654</v>
       </c>
       <c r="D3" t="n">
-        <v>22081</v>
+        <v>21427</v>
       </c>
     </row>
     <row r="4">
@@ -3599,13 +3599,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>7656</v>
+        <v>7885</v>
       </c>
       <c r="C4" t="n">
-        <v>1511</v>
+        <v>1870</v>
       </c>
       <c r="D4" t="n">
-        <v>5754</v>
+        <v>5733</v>
       </c>
     </row>
     <row r="5">
@@ -3613,13 +3613,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4262</v>
+        <v>4440</v>
       </c>
       <c r="C5" t="n">
-        <v>536</v>
+        <v>642</v>
       </c>
       <c r="D5" t="n">
-        <v>2045</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="6">
@@ -3627,13 +3627,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2399</v>
+        <v>2492</v>
       </c>
       <c r="C6" t="n">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="D6" t="n">
-        <v>1168</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="7">
@@ -3641,13 +3641,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1193</v>
+        <v>1158</v>
       </c>
       <c r="C7" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D7" t="n">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="8">
@@ -3655,13 +3655,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="C8" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D8" t="n">
-        <v>847</v>
+        <v>853</v>
       </c>
     </row>
     <row r="9">
@@ -3669,13 +3669,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
         <v>70</v>
       </c>
       <c r="D9" t="n">
-        <v>772</v>
+        <v>802</v>
       </c>
     </row>
     <row r="10">
@@ -3683,13 +3683,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="11">
@@ -3697,13 +3697,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>619</v>
+        <v>608</v>
       </c>
     </row>
     <row r="12">
@@ -3711,10 +3711,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
         <v>526</v>
@@ -3728,10 +3728,10 @@
         <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14">
@@ -3739,13 +3739,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" t="n">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15">
@@ -3753,13 +3753,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>336</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16">
@@ -3767,13 +3767,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17">
@@ -3781,13 +3781,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18">
@@ -3801,7 +3801,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19">
@@ -3809,13 +3809,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
@@ -3823,13 +3823,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -3837,13 +3837,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3882,13 +3882,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34570</v>
+        <v>35221</v>
       </c>
       <c r="C2" t="n">
-        <v>3204</v>
+        <v>3805</v>
       </c>
       <c r="D2" t="n">
-        <v>176194</v>
+        <v>169565</v>
       </c>
     </row>
     <row r="3">
@@ -3896,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15859</v>
+        <v>15817</v>
       </c>
       <c r="C3" t="n">
-        <v>3000</v>
+        <v>3582</v>
       </c>
       <c r="D3" t="n">
-        <v>26802</v>
+        <v>25958</v>
       </c>
     </row>
     <row r="4">
@@ -3910,13 +3910,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>9097</v>
+        <v>9270</v>
       </c>
       <c r="C4" t="n">
-        <v>1740</v>
+        <v>2172</v>
       </c>
       <c r="D4" t="n">
-        <v>6307</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="5">
@@ -3924,13 +3924,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5709</v>
+        <v>5910</v>
       </c>
       <c r="C5" t="n">
-        <v>701</v>
+        <v>858</v>
       </c>
       <c r="D5" t="n">
-        <v>2141</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="6">
@@ -3938,13 +3938,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3374</v>
+        <v>3500</v>
       </c>
       <c r="C6" t="n">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="D6" t="n">
-        <v>1185</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="7">
@@ -3952,13 +3952,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1837</v>
+        <v>1866</v>
       </c>
       <c r="C7" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D7" t="n">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="8">
@@ -3966,13 +3966,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>811</v>
+        <v>739</v>
       </c>
       <c r="C8" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D8" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
     </row>
     <row r="9">
@@ -3980,13 +3980,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="C9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D9" t="n">
-        <v>767</v>
+        <v>787</v>
       </c>
     </row>
     <row r="10">
@@ -3994,13 +3994,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="11">
@@ -4008,13 +4008,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>609</v>
+        <v>598</v>
       </c>
     </row>
     <row r="12">
@@ -4022,13 +4022,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="13">
@@ -4039,10 +4039,10 @@
         <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14">
@@ -4050,13 +4050,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="15">
@@ -4064,13 +4064,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16">
@@ -4078,13 +4078,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>284</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17">
@@ -4092,13 +4092,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18">
@@ -4106,13 +4106,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
         <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19">
@@ -4126,7 +4126,7 @@
         <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20">
@@ -4134,13 +4134,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
@@ -4148,13 +4148,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
